--- a/results/Int Task Remove ACC 0.1/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.1/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.041764929631038464 +/- 0.005664362257584252</t>
+          <t>0.04172689235450746 +/- 0.005698105904834285</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.03469154607768472 +/- 0.003682034539752579</t>
+          <t>0.034729626808834756 +/- 0.0037147748357219254</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.022146378460371687 +/- 0.005907055738679022</t>
+          <t>-0.02218430034129698 +/- 0.0058925526966302315</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.07465306122448977 +/- 0.0036527761831559803</t>
+          <t>0.07469387755102039 +/- 0.0036598386565648813</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.005122807017543885 +/- 0.0022587336055341803</t>
+          <t>-0.005157894736842128 +/- 0.002208297400359233</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.013774733637747338 +/- 0.004354556925698622</t>
+          <t>0.013812785388127847 +/- 0.004352062382772624</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.008295281582952818 +/- 0.005444991417529177</t>
+          <t>0.008333333333333337 +/- 0.00551015098164541</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.006571741511500584 +/- 0.00487920083893044</t>
+          <t>0.006535231836436695 +/- 0.0048557867834976235</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.003723986856516992 +/- 0.006036364420720088</t>
+          <t>0.003760496531580881 +/- 0.006014795834186522</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008806488991888706 +/- 0.0022242070372943856</t>
+          <t>0.008767864040169892 +/- 0.002232575668847953</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.004673619157976016 +/- 0.0032474834045360967</t>
+          <t>0.00471224410969483 +/- 0.003221422860099347</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.022943221320973328 +/- 0.003345910826992299</t>
+          <t>0.02298184627269214 +/- 0.0033505893342791475</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.04264759809314265 +/- 0.005994337833146431</t>
+          <t>0.042684268426842684 +/- 0.005965441703751442</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.007260726072607271 +/- 0.007430245774500292</t>
+          <t>0.00729739640630731 +/- 0.007458515103922418</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.006710671067106699 +/- 0.0018557507779802037</t>
+          <t>-0.006747341400806739 +/- 0.0018855827109911989</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>0.003410341034103437 +/- 0.0021385439401280975</t>
+          <t>0.0034470113678034763 +/- 0.002170685527971944</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0011367803447011604 +/- 0.0005549228437998342</t>
+          <t>0.0011734506784012 +/- 0.0005133846718005081</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.1588820826952527 +/- 0.005613659379255434</t>
+          <t>0.15892036753445637 +/- 0.005593911561730483</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.16125574272588059 +/- 0.0051926437467644535</t>
+          <t>0.1612174578866769 +/- 0.005245022970903509</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.15214395099540584 +/- 0.006049004594180696</t>
+          <t>0.1520673813169985 +/- 0.006139436840857917</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
